--- a/artfynd/A 51410-2023 artfynd.xlsx
+++ b/artfynd/A 51410-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51410-2023 artfynd.xlsx
+++ b/artfynd/A 51410-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152776</v>
+        <v>121152778</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474647</v>
+        <v>474669</v>
       </c>
       <c r="R4" t="n">
-        <v>6845520</v>
+        <v>6845650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152778</v>
+        <v>121152777</v>
       </c>
       <c r="B5" t="n">
-        <v>78334</v>
+        <v>78338</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474669</v>
+        <v>474671</v>
       </c>
       <c r="R5" t="n">
         <v>6845650</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152777</v>
+        <v>121152776</v>
       </c>
       <c r="B6" t="n">
-        <v>78335</v>
+        <v>91973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474671</v>
+        <v>474647</v>
       </c>
       <c r="R6" t="n">
-        <v>6845650</v>
+        <v>6845520</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 51410-2023 artfynd.xlsx
+++ b/artfynd/A 51410-2023 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152777</v>
+        <v>121152776</v>
       </c>
       <c r="B5" t="n">
-        <v>78338</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474671</v>
+        <v>474647</v>
       </c>
       <c r="R5" t="n">
-        <v>6845650</v>
+        <v>6845520</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152776</v>
+        <v>121152777</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>78338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474647</v>
+        <v>474671</v>
       </c>
       <c r="R6" t="n">
-        <v>6845520</v>
+        <v>6845650</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 51410-2023 artfynd.xlsx
+++ b/artfynd/A 51410-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152778</v>
+        <v>121152777</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474669</v>
+        <v>474671</v>
       </c>
       <c r="R4" t="n">
         <v>6845650</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152776</v>
+        <v>121152778</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474647</v>
+        <v>474669</v>
       </c>
       <c r="R5" t="n">
-        <v>6845520</v>
+        <v>6845650</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152777</v>
+        <v>121152776</v>
       </c>
       <c r="B6" t="n">
-        <v>78338</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474671</v>
+        <v>474647</v>
       </c>
       <c r="R6" t="n">
-        <v>6845650</v>
+        <v>6845520</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 51410-2023 artfynd.xlsx
+++ b/artfynd/A 51410-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152777</v>
+        <v>121152778</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474671</v>
+        <v>474669</v>
       </c>
       <c r="R4" t="n">
         <v>6845650</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152778</v>
+        <v>121152776</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
+        <v>91986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474669</v>
+        <v>474647</v>
       </c>
       <c r="R5" t="n">
-        <v>6845650</v>
+        <v>6845520</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152776</v>
+        <v>121152777</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>78341</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474647</v>
+        <v>474671</v>
       </c>
       <c r="R6" t="n">
-        <v>6845520</v>
+        <v>6845650</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 51410-2023 artfynd.xlsx
+++ b/artfynd/A 51410-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152778</v>
+        <v>121152776</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474669</v>
+        <v>474647</v>
       </c>
       <c r="R4" t="n">
-        <v>6845650</v>
+        <v>6845520</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152776</v>
+        <v>121152778</v>
       </c>
       <c r="B5" t="n">
-        <v>91986</v>
+        <v>78343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474647</v>
+        <v>474669</v>
       </c>
       <c r="R5" t="n">
-        <v>6845520</v>
+        <v>6845650</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1122,7 +1122,7 @@
         <v>121152777</v>
       </c>
       <c r="B6" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
